--- a/content/timeline.xlsx
+++ b/content/timeline.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bernardo.bozo/Desktop/Github/_THREEJS/LOK_timeline/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55CEEEC3-E2C3-134B-8E9D-5D50D1D8E4FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{017DE8CE-787D-F941-8F80-52C77A37F755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="25100" xr2:uid="{7240041B-6A59-8449-9726-667E954DD1D7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="timeline" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
   <si>
     <t>class</t>
   </si>
@@ -56,28 +56,95 @@
     <t>timeline-1</t>
   </si>
   <si>
-    <t>Lorem Ipsum</t>
-  </si>
-  <si>
-    <t>timeline-2</t>
-  </si>
-  <si>
-    <t>Dolor sit</t>
-  </si>
-  <si>
-    <t>Title example lol</t>
+    <t>Before Nosgoth's Recorded History</t>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>The Wheel of Fate</t>
+  </si>
+  <si>
+    <t>The Land of Nosgoth – ruled by the two elder races, similar in power, but different in method and intention: the Vampires, and the Hylden.</t>
+  </si>
+  <si>
+    <t>The Vampires start worshipping the &lt;b&gt;Wheel of Fate&lt;/b&gt;; a god that represents the cleansing agony of birth, death, and rebirth, the purifying rhythm of the universe – the cycle which sustains all life, to which all souls are irresistibly drawn, manipulated by the parasitic Elder God.</t>
+  </si>
+  <si>
+    <t>The Vampire-Hylden War</t>
+  </si>
+  <si>
+    <t>The Hylden oppose the Vampires’ tyrannous God, and refuse to submit to the Wheel of Fate. For this, the Vampires oppress their Hylden adversaries.</t>
+  </si>
+  <si>
+    <t>The races battle for dominance of Nosgoth in a great, apocalyptic war, which flames for a thousand years, and will destroy both victor and vanquished alike.</t>
+  </si>
+  <si>
+    <t>The Genesis of the Pillars of Nosgoth</t>
+  </si>
+  <si>
+    <t>In triumph, the Vampires banish the Hylden from the world with powerful magic, sealing them into another plane of existence, and raise the Pillars of Nosgoth as the lock that binds them.</t>
+  </si>
+  <si>
+    <t>The nine Pillars reach high into the skies, and deep into the earth (representing Mind, Dimension, Conflict, Nature, Energy, Time, States, Death, and – at the center of all of them binding them together – Balance), intrinsically and supernaturally tied to the spiritual and physical 'health' of the Land.</t>
+  </si>
+  <si>
+    <t>The Summoning of the Guardians</t>
+  </si>
+  <si>
+    <t>With the appointment of the original Vampire Guardians, the Circle of Nine – a body of sorcerers entrusted with the safekeeping of the Pillars – is formed. When a member dies, the supernatural force behind the Pillars culls a worthy successor, who is destined from birth to fulfill that role. &lt;br&gt;&lt;br&gt; Each Guardian is aligned to the principle of the Pillar he serves, and the Balance Guardian is the axis of them all.</t>
+  </si>
+  <si>
+    <t>The Blood Curse</t>
+  </si>
+  <si>
+    <t>In their defeat, the Hylden retaliate as they fall – afflicting the Vampires not only with a predatory blood-thirst, but with sterility as well</t>
+  </si>
+  <si>
+    <t>With the Vampires’ transformation comes their enemies’ true revenge: immortality. Expelled from the cycle of death and rebirth, the apostates are cast from the Wheel of Fate.</t>
+  </si>
+  <si>
+    <t>Plunged into despair, and unable to bear the separation from their God, many Vampires are driven to madness and self-annihilation.</t>
+  </si>
+  <si>
+    <t>The Forging of the Reaver</t>
+  </si>
+  <si>
+    <t>The human Vorador is born</t>
+  </si>
+  <si>
+    <t>The mystical sword known as the Blood Reaver is forged. Imbued with it's maker's lust for blood.</t>
+  </si>
+  <si>
+    <t>The Dark Gift is Passed</t>
+  </si>
+  <si>
+    <t>Vorador is turned; he becomes a vampire</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -101,8 +168,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,13 +506,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3815DBE4-1426-494D-8B3F-8B9461315769}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="138.6640625" customWidth="1"/>
+    <col min="6" max="6" width="138.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -451,64 +520,208 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
-      <c r="C2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="b">
-        <v>0</v>
-      </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/content/timeline.xlsx
+++ b/content/timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bernardo.bozo/Desktop/Github/_THREEJS/LOK_timeline/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{017DE8CE-787D-F941-8F80-52C77A37F755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{025D4AD4-E404-384C-84B7-23DCA8C47AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="25100" xr2:uid="{7240041B-6A59-8449-9726-667E954DD1D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
   <si>
     <t>class</t>
   </si>
@@ -80,9 +80,6 @@
     <t>The races battle for dominance of Nosgoth in a great, apocalyptic war, which flames for a thousand years, and will destroy both victor and vanquished alike.</t>
   </si>
   <si>
-    <t>The Genesis of the Pillars of Nosgoth</t>
-  </si>
-  <si>
     <t>In triumph, the Vampires banish the Hylden from the world with powerful magic, sealing them into another plane of existence, and raise the Pillars of Nosgoth as the lock that binds them.</t>
   </si>
   <si>
@@ -120,6 +117,30 @@
   </si>
   <si>
     <t>Vorador is turned; he becomes a vampire</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>timeline-1 detail</t>
+  </si>
+  <si>
+    <t>Millennia pass – at least 2,000 years</t>
+  </si>
+  <si>
+    <t>Nosgoth's vampire population increases</t>
+  </si>
+  <si>
+    <t>Nosgoth's early history</t>
+  </si>
+  <si>
+    <t>Over 500 years before Blood Omen: Legacy of Kain</t>
+  </si>
+  <si>
+    <t>Genesis of the Pillars of Nosgoth</t>
+  </si>
+  <si>
+    <t>The formation of the Sarafan (a monastic order of warrior-priests, charged with the eradication of the vampires) by the Circle and the crusade to counter the "vampire menace". Malek commands the armies.</t>
   </si>
 </sst>
 </file>
@@ -506,13 +527,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3815DBE4-1426-494D-8B3F-8B9461315769}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="138.6640625" customWidth="1"/>
+    <col min="7" max="7" width="138.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -529,199 +550,245 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>5</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="2" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="2" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="2" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="2" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>27</v>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/content/timeline.xlsx
+++ b/content/timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bernardo.bozo/Desktop/Github/_THREEJS/LOK_timeline/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{025D4AD4-E404-384C-84B7-23DCA8C47AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C395A97D-850E-C440-9867-85B55E801952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="25100" xr2:uid="{7240041B-6A59-8449-9726-667E954DD1D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="52">
   <si>
     <t>class</t>
   </si>
@@ -140,7 +140,58 @@
     <t>Genesis of the Pillars of Nosgoth</t>
   </si>
   <si>
-    <t>The formation of the Sarafan (a monastic order of warrior-priests, charged with the eradication of the vampires) by the Circle and the crusade to counter the "vampire menace". Malek commands the armies.</t>
+    <t>The formation of the Sarafan (a monastic order of warrior-priests, charged with the eradication of the vampires) by the Circle and the crusade to counter the "vampire menace". Malek, Guardian of the Pillar of Conflict, commands the armies.</t>
+  </si>
+  <si>
+    <t>The Vampire Purge takes place. Thousands of vampires are killed.</t>
+  </si>
+  <si>
+    <t>The Slaughter of the Circle</t>
+  </si>
+  <si>
+    <t>Janos Audron is excecuted and his heart ripped from his body</t>
+  </si>
+  <si>
+    <t>Raziel is born, and becomes a Sarafan warrior-priest</t>
+  </si>
+  <si>
+    <t>Vorador takes his revenge upon the Circle for their sponsorship of the Sarafan crusade. He infiltrates their stronghold and murders six of the sorcerers, before humiliating the Sarafan general Malek in combat.</t>
+  </si>
+  <si>
+    <t>The death of the Sarafan commanders. Raziel dies in combat, and is entombed with the Sarafan martyrs</t>
+  </si>
+  <si>
+    <t>The Necromancer Mortanius (one of the surviving Circle members, and Guardian of the Pillar of Death) punishes Malek for his failure to protect the Circle, by fusing his soul into a magical suit of armor.</t>
+  </si>
+  <si>
+    <t>The Pillars cull new successors</t>
+  </si>
+  <si>
+    <t>Vorador retreats from the world of human affairs, ensconcing himself in his remote mansion.</t>
+  </si>
+  <si>
+    <t>The Sarafan crusade ceases</t>
+  </si>
+  <si>
+    <t>History preceeding Blood Omen: Legacy of Kain</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>travel-1</t>
+  </si>
+  <si>
+    <t>Kain travels nearly 50 years into Nosgoth's past</t>
+  </si>
+  <si>
+    <t>Kain assassinates the young King William the Just, who will become the Nemesis</t>
+  </si>
+  <si>
+    <t>timeline-1 time-travel tt1</t>
+  </si>
+  <si>
+    <t>#BO-paradox-1</t>
   </si>
 </sst>
 </file>
@@ -527,268 +578,385 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3815DBE4-1426-494D-8B3F-8B9461315769}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="7" max="7" width="138.6640625" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="8" max="8" width="138.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>27</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="C9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
-      <c r="C12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>5</v>
       </c>
-      <c r="C14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>5</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>5</v>
       </c>
-      <c r="C18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>5</v>
       </c>
-      <c r="C21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>5</v>
       </c>
-      <c r="B24" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="C24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>28</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>5</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>5</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="H28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="H34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="H36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>5</v>
+      </c>
+      <c r="H37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" t="s">
+        <v>47</v>
+      </c>
+      <c r="H39" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" t="s">
+        <v>51</v>
+      </c>
+      <c r="H40" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/content/timeline.xlsx
+++ b/content/timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bernardo.bozo/Desktop/Github/_THREEJS/LOK_timeline/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C395A97D-850E-C440-9867-85B55E801952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CD360685-54F8-B545-8DB8-BE15B30DE299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="25100" xr2:uid="{7240041B-6A59-8449-9726-667E954DD1D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="60">
   <si>
     <t>class</t>
   </si>
@@ -149,9 +149,6 @@
     <t>The Slaughter of the Circle</t>
   </si>
   <si>
-    <t>Janos Audron is excecuted and his heart ripped from his body</t>
-  </si>
-  <si>
     <t>Raziel is born, and becomes a Sarafan warrior-priest</t>
   </si>
   <si>
@@ -191,7 +188,34 @@
     <t>timeline-1 time-travel tt1</t>
   </si>
   <si>
-    <t>#BO-paradox-1</t>
+    <t xml:space="preserve">timeline-1 time-travel </t>
+  </si>
+  <si>
+    <t>#paradox-1</t>
+  </si>
+  <si>
+    <t>Kain discovers another Time Streaming Device and returns to Nosgoth's present</t>
+  </si>
+  <si>
+    <t>#travel-2</t>
+  </si>
+  <si>
+    <t>timeline-2a time-travel tt3</t>
+  </si>
+  <si>
+    <t>Raziel arrives to Nosgoth's past and meets Moebius at the Sarafan fortress, now occupied by the Iron Guard, an army that seeks to avenge the Death of William the Just</t>
+  </si>
+  <si>
+    <t>entry</t>
+  </si>
+  <si>
+    <t>BO</t>
+  </si>
+  <si>
+    <t>SR2</t>
+  </si>
+  <si>
+    <t>Janos Audron is executed and his heart ripped from his body</t>
   </si>
 </sst>
 </file>
@@ -578,385 +602,419 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3815DBE4-1426-494D-8B3F-8B9461315769}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
-    <col min="8" max="8" width="138.6640625" customWidth="1"/>
+    <col min="1" max="2" width="23.33203125" customWidth="1"/>
+    <col min="9" max="9" width="138.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="b">
+      <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="b">
+      <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" t="b">
+      <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="D9" t="b">
+      <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
-      <c r="D12" t="b">
+      <c r="E12" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>5</v>
       </c>
-      <c r="D14" t="b">
+      <c r="E14" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>5</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>5</v>
       </c>
-      <c r="D18" t="b">
+      <c r="E18" t="b">
         <v>1</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>5</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="I20" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>5</v>
       </c>
-      <c r="D21" t="b">
+      <c r="E21" t="b">
         <v>1</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="I23" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>5</v>
       </c>
-      <c r="C24" t="b">
+      <c r="D24" t="b">
         <v>1</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>28</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>5</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>5</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>5</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="I31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>5</v>
-      </c>
-      <c r="H31" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>5</v>
-      </c>
-      <c r="H33" t="s">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="I34" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>5</v>
-      </c>
-      <c r="H34" t="s">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>5</v>
-      </c>
-      <c r="H35" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="I36" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>5</v>
-      </c>
-      <c r="H36" t="s">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>5</v>
+      </c>
+      <c r="I37" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>5</v>
-      </c>
-      <c r="H37" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>28</v>
       </c>
-      <c r="H38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" t="s">
+        <v>46</v>
+      </c>
+      <c r="I39" t="s">
         <v>47</v>
       </c>
-      <c r="H39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>50</v>
       </c>
-      <c r="F40" t="s">
+      <c r="B40" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40" t="s">
         <v>51</v>
       </c>
-      <c r="H40" t="s">
-        <v>49</v>
+      <c r="I40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="I42" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/content/timeline.xlsx
+++ b/content/timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bernardo.bozo/Desktop/Github/_THREEJS/LOK_timeline/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CD360685-54F8-B545-8DB8-BE15B30DE299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2C8CAAB6-7D49-C34F-B952-50D3D01019C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="25100" xr2:uid="{7240041B-6A59-8449-9726-667E954DD1D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="64">
   <si>
     <t>class</t>
   </si>
@@ -185,9 +185,6 @@
     <t>Kain assassinates the young King William the Just, who will become the Nemesis</t>
   </si>
   <si>
-    <t>timeline-1 time-travel tt1</t>
-  </si>
-  <si>
     <t xml:space="preserve">timeline-1 time-travel </t>
   </si>
   <si>
@@ -216,6 +213,21 @@
   </si>
   <si>
     <t>Janos Audron is executed and his heart ripped from his body</t>
+  </si>
+  <si>
+    <t>The Corruption of the Pillars</t>
+  </si>
+  <si>
+    <t>Mortanius, the Guardian of Death, is possessed by a dark entity</t>
+  </si>
+  <si>
+    <t>Ariel, the Guardian of Balance, is murdered; the human Kain is born, destined to take her place</t>
+  </si>
+  <si>
+    <t>Ariel's murder drives her beloved, Nupraptor (the Pillar of the Mind), insane with grief. In his agony, he unleashes a telepathic assault which ripples across the Land of Nosgoth, infecting the other members of the Circle (who are all symbiotically connected) with his madness.</t>
+  </si>
+  <si>
+    <t>timeline-1 time-travel tt1 event</t>
   </si>
 </sst>
 </file>
@@ -602,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3815DBE4-1426-494D-8B3F-8B9461315769}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="23.33203125" customWidth="1"/>
@@ -614,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>45</v>
@@ -905,7 +917,7 @@
         <v>5</v>
       </c>
       <c r="I31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
@@ -966,10 +978,10 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
         <v>46</v>
@@ -980,13 +992,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" t="s">
         <v>50</v>
-      </c>
-      <c r="B40" t="s">
-        <v>57</v>
-      </c>
-      <c r="G40" t="s">
-        <v>51</v>
       </c>
       <c r="I40" t="s">
         <v>48</v>
@@ -994,27 +1006,71 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
+        <v>57</v>
+      </c>
+      <c r="I42" t="s">
         <v>54</v>
       </c>
-      <c r="B42" t="s">
-        <v>58</v>
-      </c>
-      <c r="I42" t="s">
-        <v>55</v>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="I44" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="I45" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" t="s">
+        <v>56</v>
+      </c>
+      <c r="I46" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/content/timeline.xlsx
+++ b/content/timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bernardo.bozo/Desktop/Github/_THREEJS/LOK_timeline/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2C8CAAB6-7D49-C34F-B952-50D3D01019C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71FBF8B-7C26-774B-A389-7FE3DA0E76B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="25100" xr2:uid="{7240041B-6A59-8449-9726-667E954DD1D7}"/>
+    <workbookView xWindow="0" yWindow="560" windowWidth="40960" windowHeight="25100" xr2:uid="{7240041B-6A59-8449-9726-667E954DD1D7}"/>
   </bookViews>
   <sheets>
     <sheet name="timeline" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="82">
   <si>
     <t>class</t>
   </si>
@@ -110,15 +110,9 @@
     <t>The human Vorador is born</t>
   </si>
   <si>
-    <t>The mystical sword known as the Blood Reaver is forged. Imbued with it's maker's lust for blood.</t>
-  </si>
-  <si>
     <t>The Dark Gift is Passed</t>
   </si>
   <si>
-    <t>Vorador is turned; he becomes a vampire</t>
-  </si>
-  <si>
     <t>image</t>
   </si>
   <si>
@@ -128,15 +122,6 @@
     <t>Millennia pass – at least 2,000 years</t>
   </si>
   <si>
-    <t>Nosgoth's vampire population increases</t>
-  </si>
-  <si>
-    <t>Nosgoth's early history</t>
-  </si>
-  <si>
-    <t>Over 500 years before Blood Omen: Legacy of Kain</t>
-  </si>
-  <si>
     <t>Genesis of the Pillars of Nosgoth</t>
   </si>
   <si>
@@ -149,9 +134,6 @@
     <t>The Slaughter of the Circle</t>
   </si>
   <si>
-    <t>Raziel is born, and becomes a Sarafan warrior-priest</t>
-  </si>
-  <si>
     <t>Vorador takes his revenge upon the Circle for their sponsorship of the Sarafan crusade. He infiltrates their stronghold and murders six of the sorcerers, before humiliating the Sarafan general Malek in combat.</t>
   </si>
   <si>
@@ -179,15 +161,9 @@
     <t>travel-1</t>
   </si>
   <si>
-    <t>Kain travels nearly 50 years into Nosgoth's past</t>
-  </si>
-  <si>
     <t>Kain assassinates the young King William the Just, who will become the Nemesis</t>
   </si>
   <si>
-    <t xml:space="preserve">timeline-1 time-travel </t>
-  </si>
-  <si>
     <t>#paradox-1</t>
   </si>
   <si>
@@ -228,6 +204,84 @@
   </si>
   <si>
     <t>timeline-1 time-travel tt1 event</t>
+  </si>
+  <si>
+    <t>Human Raziel is born, and becomes a Sarafan warrior-priest</t>
+  </si>
+  <si>
+    <t>30 years pass</t>
+  </si>
+  <si>
+    <t>Vorador crafts the Reaver blade, at the behest of Janos Audron. It is the most formidable weapon ever forged by the Vampires' swordsmiths – they infuse the blade with vampiric energy, empowering the Reaver to drain their enemies of their precious lifeblood.</t>
+  </si>
+  <si>
+    <t>The Human Revolt</t>
+  </si>
+  <si>
+    <t>As the Vampires Guardians begin to die out, the Pillars summon human Guardians to fulfill their roles.</t>
+  </si>
+  <si>
+    <t>The Vampires adopt - and, when necessary, abduct - the human Guardians, and make Vampires of them when they come of age.</t>
+  </si>
+  <si>
+    <t>To sustain the Binding, the Vampires have to preserve their bloodline – and so they pass the dark gift on to the humans.</t>
+  </si>
+  <si>
+    <t>Vorador is the first human to whom the dark gift is passed, turned by the infamous Janos Audron. This is the Vampires' desperate bid to preserve their bloodline, for their enemies have cursed them not only with blood-thirst, but with sterility as well.</t>
+  </si>
+  <si>
+    <t>Moebius the Time Streamer, the Guardian of Time, and Mortanius the Necromancer, the Guardian of Death, are born. They are abducted by the Vampires, and schooled in the ancient prophecies.</t>
+  </si>
+  <si>
+    <t>Moebius is introduced to the Elder God when he lives among the Vampires of the Citadel. The Elder God speaks to Moebius even after he stops communicating with the Vampires.</t>
+  </si>
+  <si>
+    <t>A bloody revolt is orchestrated through Moebius by the Elder God. Led by Moebius and Mortanius, the humans rebel against their Vampire masters, refusing the curse and seizing the Pillars as their own.</t>
+  </si>
+  <si>
+    <t>Moebius constructs the Chronoplast and other time-streaming devices to travel to various ages of Nosgoth's history.</t>
+  </si>
+  <si>
+    <t>As the ancient Vampires' race dwindles, the humans prosper. Over the centuries, their history fades into myth, and finally recedes altogether. The humans forget them entirely, and claim the Pillars for themselves – wholly ignorant of their true purpose.</t>
+  </si>
+  <si>
+    <t>The Vampire Purge</t>
+  </si>
+  <si>
+    <t>As the Ancient Vampire race has gone extinct, human turned Vampires start increasing their numbers, their original connection with the Ancient race fades in history.</t>
+  </si>
+  <si>
+    <t>over 500 years before Blood Omen: Legacy of Kain</t>
+  </si>
+  <si>
+    <t>Some vampiric clans prey indiscriminately upon humans, attracting the attention of the Circle.</t>
+  </si>
+  <si>
+    <t>Ottmar is born. He inherits the Iron Throne of Willendorf.</t>
+  </si>
+  <si>
+    <t>William the Just is born. At a young age, he inherits rulership of a kingdom in northern Nosgoth.</t>
+  </si>
+  <si>
+    <t>The assassination of William the Just</t>
+  </si>
+  <si>
+    <t>Moebius plants another Time Streaming device at William's Castle, Kain conveniently finds said device.</t>
+  </si>
+  <si>
+    <t>Moebius arms William the Just with the Soul Reaver blade.</t>
+  </si>
+  <si>
+    <t>Kain arrives from Nosgoth's near future after using one of Moebius' Time devices, the machine is destroyed in the process.</t>
+  </si>
+  <si>
+    <t>Under Moebius's leadership, the mercenary army is formally founded, operating from the former Sarafan Stronghold.</t>
+  </si>
+  <si>
+    <t>Devastated by William's murder at the hands of a vampire, the people of William's realm swear a vengeful covenant to their fallen king, promising to eradicate Nosgoth's vampires once and for all.</t>
+  </si>
+  <si>
+    <t>timeline-1 time-travel event</t>
   </si>
 </sst>
 </file>
@@ -256,12 +310,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -276,10 +336,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,22 +696,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3815DBE4-1426-494D-8B3F-8B9461315769}">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="23.33203125" customWidth="1"/>
-    <col min="9" max="9" width="138.6640625" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="3" customWidth="1"/>
+    <col min="3" max="8" width="10.83203125" style="3"/>
+    <col min="9" max="9" width="138.6640625" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -644,433 +729,597 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="b">
+    </row>
+    <row r="25" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="b">
+      <c r="I25" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="b">
+      <c r="I33" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="I34" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" t="b">
+      <c r="I40" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" t="b">
         <v>1</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" t="b">
+      <c r="I51" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" t="s">
+        <v>48</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" t="s">
+        <v>48</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" t="s">
+        <v>48</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>48</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3"/>
+      <c r="I57" s="4"/>
+    </row>
+    <row r="58" spans="1:9" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="I13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="I15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>5</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="2" t="s">
+      <c r="I63" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>5</v>
-      </c>
-      <c r="I28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>5</v>
-      </c>
-      <c r="I29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
-      </c>
-      <c r="I30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>5</v>
-      </c>
-      <c r="I31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>5</v>
-      </c>
-      <c r="I34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>5</v>
-      </c>
-      <c r="I36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>5</v>
-      </c>
-      <c r="I37" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>28</v>
-      </c>
-      <c r="I38" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" t="s">
-        <v>46</v>
-      </c>
-      <c r="I39" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B40" t="s">
-        <v>56</v>
-      </c>
-      <c r="G40" t="s">
-        <v>50</v>
-      </c>
-      <c r="I40" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" t="s">
-        <v>56</v>
-      </c>
-      <c r="F41" t="s">
-        <v>52</v>
-      </c>
-      <c r="I41" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="I67" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="I42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" t="b">
-        <v>1</v>
-      </c>
-      <c r="I43" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44" t="s">
-        <v>56</v>
-      </c>
-      <c r="I44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" t="s">
-        <v>56</v>
-      </c>
-      <c r="I45" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>5</v>
-      </c>
-      <c r="B46" t="s">
-        <v>56</v>
-      </c>
-      <c r="I46" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
